--- a/output/b2m/b2m_aggregiert.xlsx
+++ b/output/b2m/b2m_aggregiert.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N629"/>
+  <dimension ref="A1:N628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -42346,22 +42346,22 @@
       </c>
       <c r="G606" s="3" t="inlineStr">
         <is>
-          <t>759.22</t>
+          <t>795.27</t>
         </is>
       </c>
       <c r="H606" s="3" t="inlineStr">
         <is>
-          <t>151.85</t>
+          <t>159.13</t>
         </is>
       </c>
       <c r="I606" s="3" t="inlineStr">
         <is>
-          <t>911.07</t>
+          <t>954.40</t>
         </is>
       </c>
       <c r="J606" s="4" t="inlineStr">
         <is>
-          <t>20.00%</t>
+          <t>20.01%</t>
         </is>
       </c>
       <c r="K606" s="4" t="n">
@@ -42398,12 +42398,12 @@
       </c>
       <c r="E607" s="6" t="inlineStr">
         <is>
-          <t>EETS Austria</t>
+          <t>KOSTENSTELLEN-SUMME 2</t>
         </is>
       </c>
       <c r="F607" s="6" t="inlineStr">
         <is>
-          <t>EETS Austria</t>
+          <t>KOSTENSTELLEN-SUMME 2</t>
         </is>
       </c>
       <c r="G607" s="7" t="inlineStr">
@@ -42455,32 +42455,32 @@
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>UL N 2575 E</t>
+          <t>UL N 2575E</t>
         </is>
       </c>
       <c r="E608" s="6" t="inlineStr">
         <is>
-          <t>E-charge</t>
+          <t>EETS Austria</t>
         </is>
       </c>
       <c r="F608" s="6" t="inlineStr">
         <is>
-          <t>E-charge</t>
+          <t>EETS Austria</t>
         </is>
       </c>
       <c r="G608" s="7" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>120.26</t>
         </is>
       </c>
       <c r="H608" s="7" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="I608" s="7" t="inlineStr">
         <is>
-          <t>71.35</t>
+          <t>144.31</t>
         </is>
       </c>
       <c r="J608" s="8" t="inlineStr">
@@ -42517,32 +42517,32 @@
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>UL N 2575E</t>
+          <t>UL-N 2631 E</t>
         </is>
       </c>
       <c r="E609" s="6" t="inlineStr">
         <is>
-          <t>E-charge</t>
+          <t>EETS Austria</t>
         </is>
       </c>
       <c r="F609" s="6" t="inlineStr">
         <is>
-          <t>E-charge</t>
+          <t>EETS Austria</t>
         </is>
       </c>
       <c r="G609" s="7" t="inlineStr">
         <is>
-          <t>60.80</t>
+          <t>103.37</t>
         </is>
       </c>
       <c r="H609" s="7" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="I609" s="7" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>124.04</t>
         </is>
       </c>
       <c r="J609" s="8" t="inlineStr">
@@ -42562,61 +42562,61 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="6" t="inlineStr">
-        <is>
-          <t>3603030499</t>
-        </is>
-      </c>
-      <c r="B610" s="6" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="C610" s="6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D610" s="6" t="inlineStr">
-        <is>
-          <t>UL-N 2631 E</t>
-        </is>
-      </c>
-      <c r="E610" s="6" t="inlineStr">
-        <is>
-          <t>E-charge</t>
-        </is>
-      </c>
-      <c r="F610" s="6" t="inlineStr">
-        <is>
-          <t>E-charge</t>
-        </is>
-      </c>
-      <c r="G610" s="7" t="inlineStr">
-        <is>
-          <t>103.37</t>
-        </is>
-      </c>
-      <c r="H610" s="7" t="inlineStr">
-        <is>
-          <t>20.67</t>
-        </is>
-      </c>
-      <c r="I610" s="7" t="inlineStr">
-        <is>
-          <t>124.04</t>
-        </is>
-      </c>
-      <c r="J610" s="8" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="K610" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L610" s="7" t="inlineStr"/>
-      <c r="M610" s="7" t="inlineStr"/>
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>3604122822</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>HR. MARKTHALER</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>E-charge Home</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>TR HOME CHARGE</t>
+        </is>
+      </c>
+      <c r="G610" s="3" t="inlineStr">
+        <is>
+          <t>37.93</t>
+        </is>
+      </c>
+      <c r="H610" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I610" s="3" t="inlineStr">
+        <is>
+          <t>37.93</t>
+        </is>
+      </c>
+      <c r="J610" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K610" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L610" s="3" t="inlineStr"/>
+      <c r="M610" s="3" t="inlineStr"/>
       <c r="N610" s="9" t="inlineStr">
         <is>
           <t>?</t>
@@ -42624,61 +42624,61 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="2" t="inlineStr">
+      <c r="A611" s="6" t="inlineStr">
         <is>
           <t>3604122822</t>
         </is>
       </c>
-      <c r="B611" s="2" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C611" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D611" s="2" t="inlineStr">
-        <is>
-          <t>HR. MARKTHALER</t>
-        </is>
-      </c>
-      <c r="E611" s="2" t="inlineStr">
+      <c r="B611" s="6" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C611" s="6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D611" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2376</t>
+        </is>
+      </c>
+      <c r="E611" s="6" t="inlineStr">
         <is>
           <t>E-charge Home</t>
         </is>
       </c>
-      <c r="F611" s="2" t="inlineStr">
+      <c r="F611" s="6" t="inlineStr">
         <is>
           <t>TR HOME CHARGE</t>
         </is>
       </c>
-      <c r="G611" s="3" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="H611" s="3" t="inlineStr">
+      <c r="G611" s="7" t="inlineStr">
+        <is>
+          <t>123.74</t>
+        </is>
+      </c>
+      <c r="H611" s="7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I611" s="3" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="J611" s="4" t="inlineStr">
+      <c r="I611" s="7" t="inlineStr">
+        <is>
+          <t>123.74</t>
+        </is>
+      </c>
+      <c r="J611" s="8" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K611" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L611" s="3" t="inlineStr"/>
-      <c r="M611" s="3" t="inlineStr"/>
+      <c r="K611" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L611" s="7" t="inlineStr"/>
+      <c r="M611" s="7" t="inlineStr"/>
       <c r="N611" s="9" t="inlineStr">
         <is>
           <t>?</t>
@@ -42686,61 +42686,61 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="6" t="inlineStr">
-        <is>
-          <t>3604122822</t>
-        </is>
-      </c>
-      <c r="B612" s="6" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C612" s="6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D612" s="6" t="inlineStr">
-        <is>
-          <t>UL-N 2376</t>
-        </is>
-      </c>
-      <c r="E612" s="6" t="inlineStr">
-        <is>
-          <t>E-charge Home</t>
-        </is>
-      </c>
-      <c r="F612" s="6" t="inlineStr">
-        <is>
-          <t>TR HOME CHARGE</t>
-        </is>
-      </c>
-      <c r="G612" s="7" t="inlineStr">
-        <is>
-          <t>123.74</t>
-        </is>
-      </c>
-      <c r="H612" s="7" t="inlineStr">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>3605014854</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>ERSATZKARTE 2</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>EETS CH LSVA</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>EETS CH LSVA</t>
+        </is>
+      </c>
+      <c r="G612" s="3" t="inlineStr">
+        <is>
+          <t>317.27</t>
+        </is>
+      </c>
+      <c r="H612" s="3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I612" s="7" t="inlineStr">
-        <is>
-          <t>123.74</t>
-        </is>
-      </c>
-      <c r="J612" s="8" t="inlineStr">
+      <c r="I612" s="3" t="inlineStr">
+        <is>
+          <t>317.27</t>
+        </is>
+      </c>
+      <c r="J612" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K612" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L612" s="7" t="inlineStr"/>
-      <c r="M612" s="7" t="inlineStr"/>
+      <c r="K612" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L612" s="3" t="inlineStr"/>
+      <c r="M612" s="3" t="inlineStr"/>
       <c r="N612" s="9" t="inlineStr">
         <is>
           <t>?</t>
@@ -42748,61 +42748,61 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="2" t="inlineStr">
+      <c r="A613" s="6" t="inlineStr">
         <is>
           <t>3605014854</t>
         </is>
       </c>
-      <c r="B613" s="2" t="inlineStr">
+      <c r="B613" s="6" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="C613" s="2" t="inlineStr">
+      <c r="C613" s="6" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="D613" s="2" t="inlineStr">
-        <is>
-          <t>ERSATZKARTE 2</t>
-        </is>
-      </c>
-      <c r="E613" s="2" t="inlineStr">
+      <c r="D613" s="6" t="inlineStr">
+        <is>
+          <t>RV LE 6002</t>
+        </is>
+      </c>
+      <c r="E613" s="6" t="inlineStr">
         <is>
           <t>EETS CH LSVA</t>
         </is>
       </c>
-      <c r="F613" s="2" t="inlineStr">
+      <c r="F613" s="6" t="inlineStr">
         <is>
           <t>EETS CH LSVA</t>
         </is>
       </c>
-      <c r="G613" s="3" t="inlineStr">
-        <is>
-          <t>317.27</t>
-        </is>
-      </c>
-      <c r="H613" s="3" t="inlineStr">
+      <c r="G613" s="7" t="inlineStr">
+        <is>
+          <t>2383.16</t>
+        </is>
+      </c>
+      <c r="H613" s="7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I613" s="3" t="inlineStr">
-        <is>
-          <t>317.27</t>
-        </is>
-      </c>
-      <c r="J613" s="4" t="inlineStr">
+      <c r="I613" s="7" t="inlineStr">
+        <is>
+          <t>2383.16</t>
+        </is>
+      </c>
+      <c r="J613" s="8" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K613" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L613" s="3" t="inlineStr"/>
-      <c r="M613" s="3" t="inlineStr"/>
+      <c r="K613" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L613" s="7" t="inlineStr"/>
+      <c r="M613" s="7" t="inlineStr"/>
       <c r="N613" s="9" t="inlineStr">
         <is>
           <t>?</t>
@@ -42810,61 +42810,61 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="6" t="inlineStr">
-        <is>
-          <t>3605014854</t>
-        </is>
-      </c>
-      <c r="B614" s="6" t="inlineStr">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>3605014855</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="C614" s="6" t="inlineStr">
+      <c r="C614" s="2" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="D614" s="6" t="inlineStr">
-        <is>
-          <t>RV LE 6002</t>
-        </is>
-      </c>
-      <c r="E614" s="6" t="inlineStr">
-        <is>
-          <t>EETS CH LSVA</t>
-        </is>
-      </c>
-      <c r="F614" s="6" t="inlineStr">
-        <is>
-          <t>EETS CH LSVA</t>
-        </is>
-      </c>
-      <c r="G614" s="7" t="inlineStr">
-        <is>
-          <t>2383.16</t>
-        </is>
-      </c>
-      <c r="H614" s="7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="I614" s="7" t="inlineStr">
-        <is>
-          <t>2383.16</t>
-        </is>
-      </c>
-      <c r="J614" s="8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K614" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L614" s="7" t="inlineStr"/>
-      <c r="M614" s="7" t="inlineStr"/>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>UL-N 9109 E</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>E-charge normal</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>E-charge normal</t>
+        </is>
+      </c>
+      <c r="G614" s="3" t="inlineStr">
+        <is>
+          <t>41.15</t>
+        </is>
+      </c>
+      <c r="H614" s="3" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="I614" s="3" t="inlineStr">
+        <is>
+          <t>44.48</t>
+        </is>
+      </c>
+      <c r="J614" s="4" t="inlineStr">
+        <is>
+          <t>8.09%</t>
+        </is>
+      </c>
+      <c r="K614" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L614" s="3" t="inlineStr"/>
+      <c r="M614" s="3" t="inlineStr"/>
       <c r="N614" s="9" t="inlineStr">
         <is>
           <t>?</t>
@@ -42874,52 +42874,52 @@
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>3605014855</t>
+          <t>3613014054</t>
         </is>
       </c>
       <c r="B615" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C615" s="2" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D615" s="2" t="inlineStr">
         <is>
-          <t>UL-N 9109 E</t>
+          <t>UL-N 2586 E</t>
         </is>
       </c>
       <c r="E615" s="2" t="inlineStr">
         <is>
-          <t>E-charge normal</t>
+          <t>FCharge</t>
         </is>
       </c>
       <c r="F615" s="2" t="inlineStr">
         <is>
-          <t>E-charge normal</t>
+          <t>E-charge fast</t>
         </is>
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>78.83</t>
         </is>
       </c>
       <c r="H615" s="3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="I615" s="3" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="J615" s="4" t="inlineStr">
         <is>
-          <t>8.09%</t>
+          <t>22.00%</t>
         </is>
       </c>
       <c r="K615" s="4" t="n">
@@ -42936,12 +42936,12 @@
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>3613014054</t>
+          <t>0027218036</t>
         </is>
       </c>
       <c r="B616" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C616" s="2" t="inlineStr">
@@ -42951,37 +42951,37 @@
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>UL-N 2586 E</t>
+          <t>DAH-N 303</t>
         </is>
       </c>
       <c r="E616" s="2" t="inlineStr">
         <is>
-          <t>FCharge</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F616" s="2" t="inlineStr">
         <is>
-          <t>E-charge fast</t>
+          <t>LKWDiesel</t>
         </is>
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>78.83</t>
+          <t>2731.93</t>
         </is>
       </c>
       <c r="H616" s="3" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>519.08</t>
         </is>
       </c>
       <c r="I616" s="3" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>3251.01</t>
         </is>
       </c>
       <c r="J616" s="4" t="inlineStr">
         <is>
-          <t>22.00%</t>
+          <t>19.00%</t>
         </is>
       </c>
       <c r="K616" s="4" t="n">
@@ -42996,64 +42996,72 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="2" t="inlineStr">
+      <c r="A617" s="6" t="inlineStr">
         <is>
           <t>0027218036</t>
         </is>
       </c>
-      <c r="B617" s="2" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C617" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D617" s="2" t="inlineStr">
-        <is>
-          <t>DAH-N 303</t>
-        </is>
-      </c>
-      <c r="E617" s="2" t="inlineStr">
+      <c r="B617" s="6" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C617" s="6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D617" s="6" t="inlineStr">
+        <is>
+          <t>DAH-N 314</t>
+        </is>
+      </c>
+      <c r="E617" s="6" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F617" s="2" t="inlineStr">
+      <c r="F617" s="6" t="inlineStr">
         <is>
           <t>LKWDiesel</t>
         </is>
       </c>
-      <c r="G617" s="3" t="inlineStr">
-        <is>
-          <t>2731.93</t>
-        </is>
-      </c>
-      <c r="H617" s="3" t="inlineStr">
-        <is>
-          <t>519.08</t>
-        </is>
-      </c>
-      <c r="I617" s="3" t="inlineStr">
-        <is>
-          <t>3251.01</t>
-        </is>
-      </c>
-      <c r="J617" s="4" t="inlineStr">
+      <c r="G617" s="7" t="inlineStr">
+        <is>
+          <t>1675.54</t>
+        </is>
+      </c>
+      <c r="H617" s="7" t="inlineStr">
+        <is>
+          <t>318.35</t>
+        </is>
+      </c>
+      <c r="I617" s="7" t="inlineStr">
+        <is>
+          <t>1993.89</t>
+        </is>
+      </c>
+      <c r="J617" s="8" t="inlineStr">
         <is>
           <t>19.00%</t>
         </is>
       </c>
-      <c r="K617" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L617" s="3" t="inlineStr"/>
-      <c r="M617" s="3" t="inlineStr"/>
-      <c r="N617" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="K617" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L617" s="7" t="inlineStr">
+        <is>
+          <t>1675.54</t>
+        </is>
+      </c>
+      <c r="M617" s="7" t="inlineStr">
+        <is>
+          <t>1993.89</t>
+        </is>
+      </c>
+      <c r="N617" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -43075,7 +43083,7 @@
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>DAH-N 314</t>
+          <t>DAH-N 432</t>
         </is>
       </c>
       <c r="E618" s="6" t="inlineStr">
@@ -43090,17 +43098,17 @@
       </c>
       <c r="G618" s="7" t="inlineStr">
         <is>
-          <t>1675.54</t>
+          <t>2992.16</t>
         </is>
       </c>
       <c r="H618" s="7" t="inlineStr">
         <is>
-          <t>318.35</t>
+          <t>568.51</t>
         </is>
       </c>
       <c r="I618" s="7" t="inlineStr">
         <is>
-          <t>1993.89</t>
+          <t>3560.67</t>
         </is>
       </c>
       <c r="J618" s="8" t="inlineStr">
@@ -43113,12 +43121,12 @@
       </c>
       <c r="L618" s="7" t="inlineStr">
         <is>
-          <t>1675.54</t>
+          <t>2992.16</t>
         </is>
       </c>
       <c r="M618" s="7" t="inlineStr">
         <is>
-          <t>1993.89</t>
+          <t>3560.67</t>
         </is>
       </c>
       <c r="N618" s="5" t="inlineStr">
@@ -43145,7 +43153,7 @@
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>DAH-N 432</t>
+          <t>DAH-N 654</t>
         </is>
       </c>
       <c r="E619" s="6" t="inlineStr">
@@ -43160,17 +43168,17 @@
       </c>
       <c r="G619" s="7" t="inlineStr">
         <is>
-          <t>2992.16</t>
+          <t>2454.95</t>
         </is>
       </c>
       <c r="H619" s="7" t="inlineStr">
         <is>
-          <t>568.51</t>
+          <t>466.44</t>
         </is>
       </c>
       <c r="I619" s="7" t="inlineStr">
         <is>
-          <t>3560.67</t>
+          <t>2921.39</t>
         </is>
       </c>
       <c r="J619" s="8" t="inlineStr">
@@ -43183,12 +43191,12 @@
       </c>
       <c r="L619" s="7" t="inlineStr">
         <is>
-          <t>2992.16</t>
+          <t>2454.95</t>
         </is>
       </c>
       <c r="M619" s="7" t="inlineStr">
         <is>
-          <t>3560.67</t>
+          <t>2921.39</t>
         </is>
       </c>
       <c r="N619" s="5" t="inlineStr">
@@ -43215,7 +43223,7 @@
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>DAH-N 654</t>
+          <t>DAH-N 876</t>
         </is>
       </c>
       <c r="E620" s="6" t="inlineStr">
@@ -43230,17 +43238,17 @@
       </c>
       <c r="G620" s="7" t="inlineStr">
         <is>
-          <t>2454.95</t>
+          <t>2997.55</t>
         </is>
       </c>
       <c r="H620" s="7" t="inlineStr">
         <is>
-          <t>466.44</t>
+          <t>569.53</t>
         </is>
       </c>
       <c r="I620" s="7" t="inlineStr">
         <is>
-          <t>2921.39</t>
+          <t>3567.08</t>
         </is>
       </c>
       <c r="J620" s="8" t="inlineStr">
@@ -43253,12 +43261,12 @@
       </c>
       <c r="L620" s="7" t="inlineStr">
         <is>
-          <t>2454.95</t>
+          <t>2997.55</t>
         </is>
       </c>
       <c r="M620" s="7" t="inlineStr">
         <is>
-          <t>2921.39</t>
+          <t>3567.08</t>
         </is>
       </c>
       <c r="N620" s="5" t="inlineStr">
@@ -43285,7 +43293,7 @@
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>DAH-N 876</t>
+          <t>DAH-N 902</t>
         </is>
       </c>
       <c r="E621" s="6" t="inlineStr">
@@ -43300,17 +43308,17 @@
       </c>
       <c r="G621" s="7" t="inlineStr">
         <is>
-          <t>2997.55</t>
+          <t>989.15</t>
         </is>
       </c>
       <c r="H621" s="7" t="inlineStr">
         <is>
-          <t>569.53</t>
+          <t>187.93</t>
         </is>
       </c>
       <c r="I621" s="7" t="inlineStr">
         <is>
-          <t>3567.08</t>
+          <t>1177.08</t>
         </is>
       </c>
       <c r="J621" s="8" t="inlineStr">
@@ -43323,12 +43331,12 @@
       </c>
       <c r="L621" s="7" t="inlineStr">
         <is>
-          <t>2997.55</t>
+          <t>989.15</t>
         </is>
       </c>
       <c r="M621" s="7" t="inlineStr">
         <is>
-          <t>3567.08</t>
+          <t>1177.08</t>
         </is>
       </c>
       <c r="N621" s="5" t="inlineStr">
@@ -43355,7 +43363,7 @@
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>DAH-N 902</t>
+          <t>M-AN 4903</t>
         </is>
       </c>
       <c r="E622" s="6" t="inlineStr">
@@ -43370,17 +43378,17 @@
       </c>
       <c r="G622" s="7" t="inlineStr">
         <is>
-          <t>989.15</t>
+          <t>1323.92</t>
         </is>
       </c>
       <c r="H622" s="7" t="inlineStr">
         <is>
-          <t>187.93</t>
+          <t>251.54</t>
         </is>
       </c>
       <c r="I622" s="7" t="inlineStr">
         <is>
-          <t>1177.08</t>
+          <t>1575.46</t>
         </is>
       </c>
       <c r="J622" s="8" t="inlineStr">
@@ -43393,12 +43401,12 @@
       </c>
       <c r="L622" s="7" t="inlineStr">
         <is>
-          <t>989.15</t>
+          <t>1323.92</t>
         </is>
       </c>
       <c r="M622" s="7" t="inlineStr">
         <is>
-          <t>1177.08</t>
+          <t>1575.46</t>
         </is>
       </c>
       <c r="N622" s="5" t="inlineStr">
@@ -43425,7 +43433,7 @@
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>M-AN 4903</t>
+          <t>UL-N 152</t>
         </is>
       </c>
       <c r="E623" s="6" t="inlineStr">
@@ -43440,17 +43448,17 @@
       </c>
       <c r="G623" s="7" t="inlineStr">
         <is>
-          <t>1323.92</t>
+          <t>3364.87</t>
         </is>
       </c>
       <c r="H623" s="7" t="inlineStr">
         <is>
-          <t>251.54</t>
+          <t>639.32</t>
         </is>
       </c>
       <c r="I623" s="7" t="inlineStr">
         <is>
-          <t>1575.46</t>
+          <t>4004.19</t>
         </is>
       </c>
       <c r="J623" s="8" t="inlineStr">
@@ -43463,12 +43471,12 @@
       </c>
       <c r="L623" s="7" t="inlineStr">
         <is>
-          <t>1323.92</t>
+          <t>3364.87</t>
         </is>
       </c>
       <c r="M623" s="7" t="inlineStr">
         <is>
-          <t>1575.46</t>
+          <t>4004.19</t>
         </is>
       </c>
       <c r="N623" s="5" t="inlineStr">
@@ -43495,32 +43503,32 @@
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>UL-N 152</t>
+          <t>UL-N 2339</t>
         </is>
       </c>
       <c r="E624" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>Lieferungen</t>
         </is>
       </c>
       <c r="F624" s="6" t="inlineStr">
         <is>
-          <t>LKWDiesel</t>
+          <t>Lieferungen</t>
         </is>
       </c>
       <c r="G624" s="7" t="inlineStr">
         <is>
-          <t>3364.87</t>
+          <t>85.68</t>
         </is>
       </c>
       <c r="H624" s="7" t="inlineStr">
         <is>
-          <t>639.32</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="I624" s="7" t="inlineStr">
         <is>
-          <t>4004.19</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="J624" s="8" t="inlineStr">
@@ -43533,12 +43541,12 @@
       </c>
       <c r="L624" s="7" t="inlineStr">
         <is>
-          <t>3364.87</t>
+          <t>85.68</t>
         </is>
       </c>
       <c r="M624" s="7" t="inlineStr">
         <is>
-          <t>4004.19</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="N624" s="5" t="inlineStr">
@@ -43565,32 +43573,32 @@
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>UL-N 2339</t>
+          <t>UL-N 2368</t>
         </is>
       </c>
       <c r="E625" s="6" t="inlineStr">
         <is>
-          <t>Lieferungen</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F625" s="6" t="inlineStr">
         <is>
-          <t>Lieferungen</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G625" s="7" t="inlineStr">
         <is>
-          <t>85.68</t>
+          <t>142.38</t>
         </is>
       </c>
       <c r="H625" s="7" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="I625" s="7" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>169.43</t>
         </is>
       </c>
       <c r="J625" s="8" t="inlineStr">
@@ -43603,12 +43611,12 @@
       </c>
       <c r="L625" s="7" t="inlineStr">
         <is>
-          <t>85.68</t>
+          <t>142.38</t>
         </is>
       </c>
       <c r="M625" s="7" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>169.43</t>
         </is>
       </c>
       <c r="N625" s="5" t="inlineStr">
@@ -43635,7 +43643,7 @@
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>UL-N 2368</t>
+          <t>UL-N 2560</t>
         </is>
       </c>
       <c r="E626" s="6" t="inlineStr">
@@ -43650,17 +43658,17 @@
       </c>
       <c r="G626" s="7" t="inlineStr">
         <is>
-          <t>142.38</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="H626" s="7" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="I626" s="7" t="inlineStr">
         <is>
-          <t>169.43</t>
+          <t>63.26</t>
         </is>
       </c>
       <c r="J626" s="8" t="inlineStr">
@@ -43673,12 +43681,12 @@
       </c>
       <c r="L626" s="7" t="inlineStr">
         <is>
-          <t>142.38</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="M626" s="7" t="inlineStr">
         <is>
-          <t>169.43</t>
+          <t>63.26</t>
         </is>
       </c>
       <c r="N626" s="5" t="inlineStr">
@@ -43705,7 +43713,7 @@
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>UL-N 2560</t>
+          <t>UL-N-2468</t>
         </is>
       </c>
       <c r="E627" s="6" t="inlineStr">
@@ -43720,17 +43728,17 @@
       </c>
       <c r="G627" s="7" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>89.60</t>
         </is>
       </c>
       <c r="H627" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="I627" s="7" t="inlineStr">
         <is>
-          <t>63.26</t>
+          <t>106.62</t>
         </is>
       </c>
       <c r="J627" s="8" t="inlineStr">
@@ -43743,12 +43751,12 @@
       </c>
       <c r="L627" s="7" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>89.60</t>
         </is>
       </c>
       <c r="M627" s="7" t="inlineStr">
         <is>
-          <t>63.26</t>
+          <t>106.62</t>
         </is>
       </c>
       <c r="N627" s="5" t="inlineStr">
@@ -43775,7 +43783,7 @@
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>UL-N-2468</t>
+          <t>UL-N2475</t>
         </is>
       </c>
       <c r="E628" s="6" t="inlineStr">
@@ -43790,17 +43798,17 @@
       </c>
       <c r="G628" s="7" t="inlineStr">
         <is>
-          <t>89.60</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="H628" s="7" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="I628" s="7" t="inlineStr">
         <is>
-          <t>106.62</t>
+          <t>148.75</t>
         </is>
       </c>
       <c r="J628" s="8" t="inlineStr">
@@ -43813,85 +43821,15 @@
       </c>
       <c r="L628" s="7" t="inlineStr">
         <is>
-          <t>89.60</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="M628" s="7" t="inlineStr">
         <is>
-          <t>106.62</t>
+          <t>148.75</t>
         </is>
       </c>
       <c r="N628" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" s="6" t="inlineStr">
-        <is>
-          <t>0027218036</t>
-        </is>
-      </c>
-      <c r="B629" s="6" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C629" s="6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D629" s="6" t="inlineStr">
-        <is>
-          <t>UL-N2475</t>
-        </is>
-      </c>
-      <c r="E629" s="6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="F629" s="6" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
-      <c r="G629" s="7" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="H629" s="7" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="I629" s="7" t="inlineStr">
-        <is>
-          <t>148.75</t>
-        </is>
-      </c>
-      <c r="J629" s="8" t="inlineStr">
-        <is>
-          <t>19.00%</t>
-        </is>
-      </c>
-      <c r="K629" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L629" s="7" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="M629" s="7" t="inlineStr">
-        <is>
-          <t>148.75</t>
-        </is>
-      </c>
-      <c r="N629" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -44673,9 +44611,9 @@
           <t>1880.30</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>-4333</t>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>+0</t>
         </is>
       </c>
     </row>

--- a/output/b2m/b2m_aggregiert.xlsx
+++ b/output/b2m/b2m_aggregiert.xlsx
@@ -13580,7 +13580,7 @@
       </c>
       <c r="I166" s="7" t="inlineStr">
         <is>
-          <t>2018.64</t>
+          <t>2030.13</t>
         </is>
       </c>
       <c r="J166" s="7" t="inlineStr">
@@ -13590,22 +13590,30 @@
       </c>
       <c r="K166" s="7" t="inlineStr">
         <is>
-          <t>2402.19</t>
+          <t>2413.68</t>
         </is>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
-          <t>19.00%</t>
+          <t>18.89%</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N166" s="7" t="inlineStr"/>
-      <c r="O166" s="7" t="inlineStr"/>
-      <c r="P166" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N166" s="7" t="inlineStr">
+        <is>
+          <t>2030.13</t>
+        </is>
+      </c>
+      <c r="O166" s="7" t="inlineStr">
+        <is>
+          <t>2413.68</t>
+        </is>
+      </c>
+      <c r="P166" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -53061,12 +53069,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>18475.48</t>
+          <t>20505.61</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>21986.00</t>
+          <t>24399.68</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -53091,7 +53099,7 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>-3096</t>
+          <t>-1947</t>
         </is>
       </c>
     </row>

--- a/output/b2m/b2m_aggregiert.xlsx
+++ b/output/b2m/b2m_aggregiert.xlsx
@@ -13585,17 +13585,17 @@
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>383.55</t>
+          <t>385.73</t>
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr">
         <is>
-          <t>2413.68</t>
+          <t>2415.86</t>
         </is>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
-          <t>18.89%</t>
+          <t>19.00%</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="O166" s="7" t="inlineStr">
         <is>
-          <t>2413.68</t>
+          <t>2415.86</t>
         </is>
       </c>
       <c r="P166" s="5" t="inlineStr">
@@ -53074,7 +53074,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>24399.68</t>
+          <t>24401.86</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>-1947</t>
+          <t>-1729</t>
         </is>
       </c>
     </row>

--- a/output/b2m/b2m_aggregiert.xlsx
+++ b/output/b2m/b2m_aggregiert.xlsx
@@ -69,12 +69,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00FFB3B3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB3B3"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,11 +114,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,7 +134,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,7 +152,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -17201,11 +17201,19 @@
       <c r="M211" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N211" s="7" t="inlineStr"/>
-      <c r="O211" s="7" t="inlineStr"/>
-      <c r="P211" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N211" s="7" t="inlineStr">
+        <is>
+          <t>467.59</t>
+        </is>
+      </c>
+      <c r="O211" s="7" t="inlineStr">
+        <is>
+          <t>556.43</t>
+        </is>
+      </c>
+      <c r="P211" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -18473,11 +18481,19 @@
       <c r="M227" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N227" s="7" t="inlineStr"/>
-      <c r="O227" s="7" t="inlineStr"/>
-      <c r="P227" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N227" s="7" t="inlineStr">
+        <is>
+          <t>123.07</t>
+        </is>
+      </c>
+      <c r="O227" s="7" t="inlineStr">
+        <is>
+          <t>146.45</t>
+        </is>
+      </c>
+      <c r="P227" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -18764,32 +18780,40 @@
       </c>
       <c r="I231" s="7" t="inlineStr">
         <is>
-          <t>164.50</t>
+          <t>178.60</t>
         </is>
       </c>
       <c r="J231" s="7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>33.92</t>
         </is>
       </c>
       <c r="K231" s="7" t="inlineStr">
         <is>
-          <t>195.75</t>
+          <t>212.52</t>
         </is>
       </c>
       <c r="L231" s="8" t="inlineStr">
         <is>
-          <t>19.00%</t>
+          <t>18.99%</t>
         </is>
       </c>
       <c r="M231" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N231" s="7" t="inlineStr"/>
-      <c r="O231" s="7" t="inlineStr"/>
-      <c r="P231" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N231" s="7" t="inlineStr">
+        <is>
+          <t>178.60</t>
+        </is>
+      </c>
+      <c r="O231" s="7" t="inlineStr">
+        <is>
+          <t>212.52</t>
+        </is>
+      </c>
+      <c r="P231" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -19577,11 +19601,19 @@
       <c r="M241" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N241" s="7" t="inlineStr"/>
-      <c r="O241" s="7" t="inlineStr"/>
-      <c r="P241" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N241" s="7" t="inlineStr">
+        <is>
+          <t>153.76</t>
+        </is>
+      </c>
+      <c r="O241" s="7" t="inlineStr">
+        <is>
+          <t>182.97</t>
+        </is>
+      </c>
+      <c r="P241" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -20049,11 +20081,19 @@
       <c r="M247" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N247" s="7" t="inlineStr"/>
-      <c r="O247" s="7" t="inlineStr"/>
-      <c r="P247" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N247" s="7" t="inlineStr">
+        <is>
+          <t>61.10</t>
+        </is>
+      </c>
+      <c r="O247" s="7" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="P247" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -20281,11 +20321,19 @@
       <c r="M250" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N250" s="7" t="inlineStr"/>
-      <c r="O250" s="7" t="inlineStr"/>
-      <c r="P250" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N250" s="7" t="inlineStr">
+        <is>
+          <t>511.31</t>
+        </is>
+      </c>
+      <c r="O250" s="7" t="inlineStr">
+        <is>
+          <t>608.46</t>
+        </is>
+      </c>
+      <c r="P250" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -20353,11 +20401,19 @@
       <c r="M251" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N251" s="7" t="inlineStr"/>
-      <c r="O251" s="7" t="inlineStr"/>
-      <c r="P251" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N251" s="7" t="inlineStr">
+        <is>
+          <t>196.78</t>
+        </is>
+      </c>
+      <c r="O251" s="7" t="inlineStr">
+        <is>
+          <t>234.17</t>
+        </is>
+      </c>
+      <c r="P251" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -22025,11 +22081,19 @@
       <c r="M272" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N272" s="7" t="inlineStr"/>
-      <c r="O272" s="7" t="inlineStr"/>
-      <c r="P272" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N272" s="7" t="inlineStr">
+        <is>
+          <t>168.82</t>
+        </is>
+      </c>
+      <c r="O272" s="7" t="inlineStr">
+        <is>
+          <t>200.90</t>
+        </is>
+      </c>
+      <c r="P272" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -22337,11 +22401,19 @@
       <c r="M276" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N276" s="7" t="inlineStr"/>
-      <c r="O276" s="7" t="inlineStr"/>
-      <c r="P276" s="9" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="N276" s="7" t="inlineStr">
+        <is>
+          <t>196.78</t>
+        </is>
+      </c>
+      <c r="O276" s="7" t="inlineStr">
+        <is>
+          <t>234.17</t>
+        </is>
+      </c>
+      <c r="P276" s="10" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -53069,12 +53141,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>20505.61</t>
+          <t>22563.42</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>24401.86</t>
+          <t>26850.64</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -53097,9 +53169,9 @@
           <t>27100.77</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>-1729</t>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>-52</t>
         </is>
       </c>
     </row>

--- a/output/b2m/b2m_aggregiert.xlsx
+++ b/output/b2m/b2m_aggregiert.xlsx
@@ -45,7 +45,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +82,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -152,7 +157,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -53838,14 +53845,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
@@ -54081,7 +54088,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>— (5x split-block recovered)</t>
+          <t>5x split-block recovered</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -54118,12 +54125,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>RV LE 6002 (K1=? split-block)</t>
+          <t>UL-N2423E Mischsteuer (K1=✗ ok)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>27064.99</t>
+          <t>27100.25</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -54133,12 +54140,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>-3096</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>RV LE 6002 kein kz_summen, Betrag unklar</t>
+          <t>-52</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>Sonstiges 0% USt + Kraftstoffe 19% — strukturell, kein Fehler</t>
         </is>
       </c>
     </row>
@@ -54155,7 +54162,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>— (residual nach allen Fixes)</t>
+          <t>9x K1=? ohne SUMME KARTE</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -54173,9 +54180,9 @@
           <t>+30227</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>Übererfassung, Ursache unklar — Carlos prüft</t>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Offene Positionen — manuelle Prüfung erforderlich (siehe Sektion C)</t>
         </is>
       </c>
     </row>
@@ -54192,7 +54199,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>— (residual nach allen Fixes)</t>
+          <t>10x K1=? ohne SUMME KARTE</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -54210,11 +54217,606 @@
           <t>+14523</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>Übererfassung, Ursache unklar — Carlos prüft</t>
-        </is>
-      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Offene Positionen — manuelle Prüfung erforderlich (siehe Sektion C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>C) Offene K1=? Positionen — SUMME KARTE/KFZ fehlt, manuelle Verifikation erforderlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>PDF-Datei</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Rechnungsnummer</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Seite</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Kennzeichen</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Σ Netto Vision</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>SUMME KARTE Netto</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>Δ Netto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>UL-N 2364</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>468.64</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2359</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>410.87</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2559</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>301.41</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2513</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>266.24</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2625</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>201.97</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr"/>
+      <c r="G23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2594</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>156.43</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 1022</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>114.15</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2608</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>92.31</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr"/>
+      <c r="G26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B2M 3 1.pdf</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>0027134312</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2481 E</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>54.95</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>UL-N 2499E</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>447.17</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>BS-OR 3796</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>267.82</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr"/>
+      <c r="G29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2528</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>233.72</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>UL N 2432</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>157.27</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2458</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>171.70</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr"/>
+      <c r="G32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2336</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>153.71</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>BS-OR 1713</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>104.28</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2608</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>88.05</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 2483E</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>34.38</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr"/>
+      <c r="G36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B2M 4 1.pdf</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>0027192675</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>UL-N 1200 E</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>4.99</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr"/>
+      <c r="G37" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
